--- a/評価シート改訂案/改訂案_比較と進め方.xlsx
+++ b/評価シート改訂案/改訂案_比較と進め方.xlsx
@@ -95,7 +95,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -117,11 +117,55 @@
         <color rgb="00A6A6A6"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00A6A6A6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A6A6A6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00A6A6A6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A6A6A6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -148,6 +192,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -529,9 +575,9 @@
           <t>評価シート改訂案　比較表（この表を見て選ぶだけ）</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="11" t="n"/>
     </row>
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
@@ -656,7 +702,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>S・B以下は事実の記入が必須。事実が書けない評価は付けられない</t>
+          <t>Aを含むすべての項目に事実の記入が必須（書けない項目はB）。総合Aは成果の数字が伴わないと届かない（75点以上）</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -766,7 +812,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>見た目が大きく変わるため説明会が必要。その分「変わった感」があり納得を得やすい</t>
+          <t>見た目は大きく変わるが、定義と使い方はシート内に記載済み。「変わった感」があり納得を得やすい</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -803,9 +849,9 @@
           <t>おすすめは案A：「点数じゃなくてSABCDの方がいいのでは？」という現場の声にそのまま応える案で、評価の説明（基準・事実・評価の3点セット）が最もやりやすい。ただし案Bも全ての問題点に対応済みなので、現行からの変化を小さくしたい場合は案B→次々期に案Aの2段階が現実的。</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -814,7 +860,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -839,8 +885,8 @@
           <t>導入の進め方（小さく始めて、運用しながら直す）</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="11" t="n"/>
     </row>
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
@@ -867,7 +913,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>「日々の記録（月次ログ）」だけ先に全部署で始める</t>
+          <t>「日々の記録（月次ログ）」を先に使い始める（各課の判断で可）</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -884,12 +930,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>案A・案Bを幹部＋各部署代表で検討し、どちらかに決定</t>
+          <t>案A・案Bのどちらにするかを社長に決めていただく</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>この比較表を見ながら30分の会議で決める。決めきれない場合は案B（現行の延長）から始めて、次々期に案Aへ進む2段階でもよい</t>
+          <t>この比較表を見て選ぶだけでよい。決めきれない場合は案B（現行の延長）から始めて、次々期に案Aへ進む2段階でもよい</t>
         </is>
       </c>
     </row>
@@ -901,12 +947,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>全員向け説明会（30分）＋評価者の目線合わせ会議（30分）</t>
+          <t>新シートを配布する（「改訂のポイント」「評価基準の定義」シートを同封）</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>「A（7点）＝期待どおり＝良い評価」「S（10点）には事実が必要」という考え方を全員に伝える。ここを省くと『厳しくなった』と誤解される</t>
+          <t>「期待どおりが標準」「評価には事実が必要」という考え方はシート内に記載済みのため、別途の説明の場を設けなくても運用できる</t>
         </is>
       </c>
     </row>
@@ -923,7 +969,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>初回は処遇への反映を現行ルールのまま慎重に行い、評価のばらつきを確認する。評価後に必ず10〜15分のフィードバック面談を行う</t>
+          <t>初回は処遇への反映を現行ルールのまま慎重に行い、評価のばらつきを確認する</t>
         </is>
       </c>
     </row>
@@ -935,7 +981,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>評価者・被評価者双方に感想を聞き、項目・基準を微調整</t>
+          <t>必要があれば、次の期に項目・基準を見直す</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -950,8 +996,8 @@
           <t>■ 運用の合言葉</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="11" t="n"/>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="B12" s="9" t="inlineStr">
@@ -959,8 +1005,8 @@
           <t>・「A（期待どおり）は良い評価」— 満点思想をやめる。これを全員が理解すれば『なぜ満点じゃないのか』問題はなくなる</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="11" t="n"/>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="B13" s="9" t="inlineStr">
@@ -968,17 +1014,17 @@
           <t>・「事実が書けない評価は付けない」— 感情・印象の入り込みを防ぐ唯一のルール</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="11" t="n"/>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>・「評価は面談で完結」— シートを渡して終わりにしない。10分の面談が評価制度の納得感のほぼ全てを決める</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
+          <t>・「判定はExcel、決定は社長」— 評価者は事実を書いて記号を選ぶだけ。手間は今より増えない</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="11" t="n"/>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="B15" s="9" t="inlineStr">
@@ -986,8 +1032,8 @@
           <t>・「完璧を待たない」— まず月次ログから。制度は運用しながら直す</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1000,6 +1046,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>